--- a/inputs/templates/TEMPLATE_FONDO_LIQUIDEZ_Permanente.xlsx
+++ b/inputs/templates/TEMPLATE_FONDO_LIQUIDEZ_Permanente.xlsx
@@ -2301,11 +2301,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="93946477"/>
-        <c:axId val="86093166"/>
+        <c:axId val="90963364"/>
+        <c:axId val="93290171"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="93946477"/>
+        <c:axId val="90963364"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="43373"/>
@@ -2339,7 +2339,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="86093166"/>
+        <c:crossAx val="93290171"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
@@ -2351,7 +2351,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="86093166"/>
+        <c:axId val="93290171"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="100"/>
@@ -2394,7 +2394,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="93946477"/>
+        <c:crossAx val="90963364"/>
         <c:crossesAt val="38687"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3276,11 +3276,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="65673707"/>
-        <c:axId val="54962828"/>
+        <c:axId val="18325022"/>
+        <c:axId val="68060782"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="65673707"/>
+        <c:axId val="18325022"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3312,14 +3312,14 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="54962828"/>
+        <c:crossAx val="68060782"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
         <c:noMultiLvlLbl val="0"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="54962828"/>
+        <c:axId val="68060782"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="100"/>
@@ -3393,7 +3393,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="65673707"/>
+        <c:crossAx val="18325022"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="5"/>
@@ -7365,7 +7365,7 @@
       </c>
       <c r="AW20" s="33" t="n">
         <f aca="false">LOOKUP(AW19,$A$3:$A$2973,$B$3:$B$2973)</f>
-        <v>19635.3400812264</v>
+        <v>19916.8502383877</v>
       </c>
       <c r="AX20" s="33" t="n">
         <f aca="false">LOOKUP(AX19,$A$3:$A$2973,$B$3:$B$2973)</f>
@@ -7618,7 +7618,7 @@
       </c>
       <c r="AH22" s="22" t="n">
         <f aca="false">+S23/R23-1</f>
-        <v>-0.254362857499898</v>
+        <v>-0.243672722859896</v>
       </c>
       <c r="AI22" s="9"/>
       <c r="AJ22" s="9"/>
@@ -7630,7 +7630,7 @@
       <c r="AP22" s="9"/>
       <c r="AQ22" s="23" t="n">
         <f aca="false">+(S23/P23-1)/COUNTA(AE22:AP22)*12</f>
-        <v>-0.746250693705866</v>
+        <v>-0.71393888658704</v>
       </c>
       <c r="AV22" s="28" t="s">
         <v>27</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="S23" s="3" t="n">
         <f aca="false">+B249</f>
-        <v>19635.3400812264</v>
+        <v>19916.8502383877</v>
       </c>
       <c r="U23" s="19"/>
       <c r="Y23" s="19"/>
@@ -8182,23 +8182,23 @@
       </c>
       <c r="AX29" s="43" t="n">
         <f aca="false">$AW20/AX20-1</f>
-        <v>-0.254362857499898</v>
+        <v>-0.243672722859896</v>
       </c>
       <c r="AY29" s="43" t="n">
         <f aca="false">$AW20/AY20-1</f>
-        <v>-0.248750231235289</v>
+        <v>-0.237979628862347</v>
       </c>
       <c r="AZ29" s="43" t="n">
         <f aca="false">$AW20/AZ20-1</f>
-        <v>-0.239809516977627</v>
+        <v>-0.228910732364632</v>
       </c>
       <c r="BA29" s="43" t="n">
         <f aca="false">$AW20/BA20-1</f>
-        <v>-0.220741912237796</v>
+        <v>-0.209569757039683</v>
       </c>
       <c r="BB29" s="43" t="n">
         <f aca="false">+AQ86</f>
-        <v>-0.746250693705866</v>
+        <v>-0.71393888658704</v>
       </c>
       <c r="BC29" s="44"/>
       <c r="BD29" s="27"/>
@@ -12238,7 +12238,7 @@
       </c>
       <c r="AH86" s="60" t="n">
         <f aca="false">+AH22</f>
-        <v>-0.254362857499898</v>
+        <v>-0.243672722859896</v>
       </c>
       <c r="AI86" s="60"/>
       <c r="AJ86" s="60"/>
@@ -12250,7 +12250,7 @@
       <c r="AP86" s="60"/>
       <c r="AQ86" s="60" t="n">
         <f aca="false">+AQ22</f>
-        <v>-0.746250693705866</v>
+        <v>-0.71393888658704</v>
       </c>
     </row>
     <row r="87" s="4" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17871,15 +17871,15 @@
         <v>46142</v>
       </c>
       <c r="B249" s="3" t="n">
-        <v>19635.3400812264</v>
+        <v>19916.8502383877</v>
       </c>
       <c r="C249" s="25" t="n">
         <f aca="false">(B249/B248-1)/(A249-A248)*30</f>
-        <v>-0.254362857499898</v>
+        <v>-0.243672722859896</v>
       </c>
       <c r="D249" s="19" t="n">
         <f aca="false">+D248*(1+C249)</f>
-        <v>86.8834625739727</v>
+        <v>88.1291031945447</v>
       </c>
       <c r="F249" s="17" t="n">
         <v>46142</v>
@@ -18006,15 +18006,15 @@
       </c>
       <c r="T2" s="81" t="n">
         <f aca="false">+'Datos ICP (2)'!AX29</f>
-        <v>-0.254362857499898</v>
+        <v>-0.243672722859896</v>
       </c>
       <c r="U2" s="81" t="n">
         <f aca="false">+'Datos ICP (2)'!AY29</f>
-        <v>-0.248750231235289</v>
+        <v>-0.237979628862347</v>
       </c>
       <c r="V2" s="81" t="n">
         <f aca="false">+'Datos ICP (2)'!AZ29</f>
-        <v>-0.239809516977627</v>
+        <v>-0.228910732364632</v>
       </c>
       <c r="W2" s="81" t="n">
         <f aca="false">+Q33</f>
@@ -18022,7 +18022,7 @@
       </c>
       <c r="X2" s="81" t="n">
         <f aca="false">+'Datos ICP (2)'!BB29</f>
-        <v>-0.746250693705866</v>
+        <v>-0.71393888658704</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19354,7 +19354,7 @@
       </c>
       <c r="H39" s="87" t="n">
         <f aca="false">+'Datos ICP (2)'!AH86</f>
-        <v>-0.254362857499898</v>
+        <v>-0.243672722859896</v>
       </c>
       <c r="I39" s="87"/>
       <c r="J39" s="87"/>
@@ -19366,7 +19366,7 @@
       <c r="P39" s="87"/>
       <c r="Q39" s="87" t="n">
         <f aca="false">+'Datos ICP (2)'!AQ86</f>
-        <v>-0.746250693705866</v>
+        <v>-0.71393888658704</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/inputs/templates/TEMPLATE_FONDO_LIQUIDEZ_Permanente.xlsx
+++ b/inputs/templates/TEMPLATE_FONDO_LIQUIDEZ_Permanente.xlsx
@@ -2301,11 +2301,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="90963364"/>
-        <c:axId val="93290171"/>
+        <c:axId val="34067767"/>
+        <c:axId val="51097812"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="90963364"/>
+        <c:axId val="34067767"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="43373"/>
@@ -2339,7 +2339,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="93290171"/>
+        <c:crossAx val="51097812"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
@@ -2351,7 +2351,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="93290171"/>
+        <c:axId val="51097812"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="100"/>
@@ -2394,7 +2394,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="90963364"/>
+        <c:crossAx val="34067767"/>
         <c:crossesAt val="38687"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3276,11 +3276,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="18325022"/>
-        <c:axId val="68060782"/>
+        <c:axId val="48831318"/>
+        <c:axId val="44894659"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="18325022"/>
+        <c:axId val="48831318"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3312,14 +3312,14 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="68060782"/>
+        <c:crossAx val="44894659"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
         <c:noMultiLvlLbl val="0"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="68060782"/>
+        <c:axId val="44894659"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="100"/>
@@ -3393,7 +3393,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="18325022"/>
+        <c:crossAx val="48831318"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="5"/>

--- a/inputs/templates/TEMPLATE_FONDO_LIQUIDEZ_Permanente.xlsx
+++ b/inputs/templates/TEMPLATE_FONDO_LIQUIDEZ_Permanente.xlsx
@@ -2301,11 +2301,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="34067767"/>
-        <c:axId val="51097812"/>
+        <c:axId val="3770348"/>
+        <c:axId val="79250218"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="34067767"/>
+        <c:axId val="3770348"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="43373"/>
@@ -2339,7 +2339,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="51097812"/>
+        <c:crossAx val="79250218"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
@@ -2351,7 +2351,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="51097812"/>
+        <c:axId val="79250218"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="100"/>
@@ -2394,7 +2394,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="34067767"/>
+        <c:crossAx val="3770348"/>
         <c:crossesAt val="38687"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3276,11 +3276,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="48831318"/>
-        <c:axId val="44894659"/>
+        <c:axId val="24288453"/>
+        <c:axId val="10566734"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="48831318"/>
+        <c:axId val="24288453"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3312,14 +3312,14 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="44894659"/>
+        <c:crossAx val="10566734"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
         <c:noMultiLvlLbl val="0"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="44894659"/>
+        <c:axId val="10566734"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="100"/>
@@ -3393,7 +3393,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="48831318"/>
+        <c:crossAx val="24288453"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="5"/>

--- a/inputs/templates/TEMPLATE_FONDO_LIQUIDEZ_Permanente.xlsx
+++ b/inputs/templates/TEMPLATE_FONDO_LIQUIDEZ_Permanente.xlsx
@@ -2301,11 +2301,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="3770348"/>
-        <c:axId val="79250218"/>
+        <c:axId val="94868494"/>
+        <c:axId val="32757965"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="3770348"/>
+        <c:axId val="94868494"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="43373"/>
@@ -2339,7 +2339,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="79250218"/>
+        <c:crossAx val="32757965"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
@@ -2351,7 +2351,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="79250218"/>
+        <c:axId val="32757965"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="100"/>
@@ -2394,7 +2394,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="3770348"/>
+        <c:crossAx val="94868494"/>
         <c:crossesAt val="38687"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3276,11 +3276,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="24288453"/>
-        <c:axId val="10566734"/>
+        <c:axId val="77652235"/>
+        <c:axId val="51611936"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="24288453"/>
+        <c:axId val="77652235"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3312,14 +3312,14 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="10566734"/>
+        <c:crossAx val="51611936"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
         <c:noMultiLvlLbl val="0"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="10566734"/>
+        <c:axId val="51611936"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="100"/>
@@ -3393,7 +3393,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="24288453"/>
+        <c:crossAx val="77652235"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="5"/>
